--- a/Students Semester Result.xlsx
+++ b/Students Semester Result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\All Folders\Python Lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D341F40-7A81-4A42-A01D-83C816B4E67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9A652C-8719-4902-83D7-DA23A5D4867F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{84F156D0-258B-4DB8-BC55-6A55B7737425}"/>
   </bookViews>
